--- a/data/kz/niches/niche_formats_BROW.xlsx
+++ b/data/kz/niches/niche_formats_BROW.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -595,7 +596,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -641,12 +642,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BROW_RENT</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -692,12 +693,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -768,6 +769,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,12 +825,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -861,12 +863,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -899,12 +901,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -969,6 +971,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1019,12 +1022,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1056,12 +1059,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1124,6 +1127,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1223,6 +1227,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1537,6 +1542,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1662,6 +1668,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1747,7 +1754,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1801,12 +1808,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_RENT</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1860,12 +1867,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1965,6 +1972,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2090,7 +2098,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2160,12 +2168,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_RENT</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2235,12 +2243,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2346,6 +2354,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2421,7 +2430,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2459,12 +2468,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_RENT</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2502,12 +2511,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2581,6 +2590,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2656,7 +2666,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2696,12 +2706,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_RENT</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2741,12 +2751,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2819,6 +2829,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2879,7 +2890,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2916,12 +2927,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_RENT</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2958,12 +2969,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3036,6 +3047,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3111,7 +3123,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3167,12 +3179,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_RENT</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3228,12 +3240,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3320,6 +3332,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3383,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3404,7 +3417,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3438,7 +3451,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3472,7 +3485,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3528,6 +3541,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3553,12 +3567,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3575,12 +3589,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
